--- a/data/tags/אלבומים חדשים/global/2026-02-week02/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>NEVER ENOUGH של טרנסטייל הוכתר כאלבום הרוק הטוב ביותר בגראמי</v>
+        <v>עברי לידר – אין לך מילה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/never-enough-%d7%a9%d7%9c-%d7%98%d7%a8%d7%a0%d7%a1%d7%98%d7%99%d7%99%d7%9c-%d7%94%d7%95%d7%9b%d7%aa%d7%a8-%d7%9b%d7%90%d7%9c%d7%91%d7%95%d7%9d-%d7%94%d7%a8%d7%95%d7%a7-%d7%94%d7%98%d7%95%d7%91-%d7%91/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%91%d7%a8%d7%99-%d7%9c%d7%99%d7%93%d7%a8-%d7%90%d7%99%d7%9f-%d7%9c%d7%9a-%d7%9e%d7%99%d7%9c%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום רחב היריעה הוא התפתחות חסרת מנוחה ומלהיבה של הצליל שובר־הז’אנרים של הלהקה. זהו מסע טרנספורמטיבי – חסר פחד ומלא חיים – של אחת הלהקות החדשניות והמשפיעות ביותר בדור שלה. טרנסטייל (Turnstile) מגיעים מהארדקור של בולטימור, אבל ב־NEVER ENOUGH הם</v>
+        <v>ה-EP "אין לך מילה" של עברי לידר הוא מהלך אמנותי חריג ומשמעותי בקריירה שלו – גם בגלל הוויתור על כתיבה אישית לטובת טל קסטיאל, וגם בגלל האימוץ המלא של קול נשי כנקודת מוצא רגשית. זה לא “רק” שינוי טקסטואלי –</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>NEVER ENOUGH של טרנסטייל הוכתר כאלבום הרוק הטוב ביותר בגראמי</v>
+        <v>עברי לידר – אין לך מילה</v>
       </c>
     </row>
   </sheetData>
